--- a/KAMCHATKA_FINAL_ZAVODY/00_СВОДКА.xlsx
+++ b/KAMCHATKA_FINAL_ZAVODY/00_СВОДКА.xlsx
@@ -547,7 +547,11 @@
           <t>ООО «Восточная арматурная компания»</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>+7 (347) 226-00-00 kontakt@vark.ru</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
         <v>20</v>
       </c>
@@ -630,7 +634,11 @@
           <t>ООО ПИК «АЛГРУПП»</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>8-800-200-52-76 info@pik-algrupp.ru</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n">
         <v>10</v>
       </c>
@@ -655,7 +663,11 @@
           <t>ООО «Бологовский арматурный завод» (ТМ «БАЗ», латунная арматура)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>+7 (48238) 2-21-13 (завод, Бологое) sales@bolarm.com (продажи)</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
         <v>9</v>
       </c>
@@ -1028,7 +1040,11 @@
           <t>ООО ПКФ «Экс-Форма»</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>8-800-550-52-31 exform@exform.ru</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="n">
         <v>1</v>
       </c>
